--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5708ABC0-48CE-4829-A416-575AB020A4AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83904DF0-BC36-435B-96E8-FE1E188B0D74}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E3E86FA-45BF-401F-8712-A246E0D57B30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8DA24CF-D5FC-45D4-82BB-E3BF08AE8C4E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E0AA927-D512-4C5A-B807-B8E721597CF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F43E821-8387-4339-8C26-0F8B4EF07935}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83904DF0-BC36-435B-96E8-FE1E188B0D74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A7B9E40-FEFF-4BD5-9529-30D9268428E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8DA24CF-D5FC-45D4-82BB-E3BF08AE8C4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EEFB24D-F8AF-4426-9958-06243FBBB668}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F43E821-8387-4339-8C26-0F8B4EF07935}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E2C84D6-64E9-42B0-9DAD-8A90F40D1DD5}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A7B9E40-FEFF-4BD5-9529-30D9268428E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5708ABC0-48CE-4829-A416-575AB020A4AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EEFB24D-F8AF-4426-9958-06243FBBB668}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E3E86FA-45BF-401F-8712-A246E0D57B30}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E2C84D6-64E9-42B0-9DAD-8A90F40D1DD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E0AA927-D512-4C5A-B807-B8E721597CF7}"/>
 </file>